--- a/artfynd/A 59610-2023 artfynd.xlsx
+++ b/artfynd/A 59610-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59610-2023 artfynd.xlsx
+++ b/artfynd/A 59610-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14970648</v>
+        <v>14970641</v>
       </c>
       <c r="B2" t="n">
-        <v>9302</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -720,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>funnen död</t>
+          <t>frispringande/krypande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419348.2022857282</v>
+        <v>419339</v>
       </c>
       <c r="R2" t="n">
-        <v>6159751.399279575</v>
+        <v>6159813</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:49</t>
+          <t>00:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:49</t>
+          <t>00:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,15 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>14970647</v>
+        <v>14970642</v>
       </c>
       <c r="B3" t="n">
-        <v>9302</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,7 +829,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -851,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>419351.9270630887</v>
+        <v>419350</v>
       </c>
       <c r="R3" t="n">
-        <v>6159738.329059703</v>
+        <v>6159802</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:43</t>
+          <t>00:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,16 +900,11 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:43</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ej återfunnen, obs. 2003-2007</t>
+          <t>00:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
@@ -925,6 +924,258 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>14970644</v>
+      </c>
+      <c r="B4" t="n">
+        <v>9406</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NV Snogeholmssjön, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>419353</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6159793</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sjöbo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sövde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2008-06-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>00:32</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2008-06-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>00:32</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>14970648</v>
+      </c>
+      <c r="B5" t="n">
+        <v>9406</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NV Snogeholmssjön, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>419348</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6159751</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sjöbo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sövde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2008-06-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>00:49</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2008-06-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>00:49</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Boris Berglund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
